--- a/12624865.xlsx
+++ b/12624865.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\LPU\sem1\python\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\GIT_DEMO\CAP-776\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E0652E-2227-47A5-AF2E-0B21CF23AB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1DC871B-5CD1-4D7F-B680-063919809035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -228,6 +228,12 @@
   <si>
     <t>nicee!!</t>
   </si>
+  <si>
+    <t>Day was hectic!!</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
 </sst>
 </file>
 
@@ -409,10 +415,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -920,35 +926,35 @@
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="21">
         <v>12624865</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="G3" s="21"/>
+      <c r="G3" s="20"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
@@ -1244,7 +1250,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B11" s="14">
         <v>360</v>
@@ -1264,134 +1270,258 @@
       <c r="G11" s="14">
         <v>0</v>
       </c>
-      <c r="H11" s="14"/>
+      <c r="H11" s="14">
+        <v>300</v>
+      </c>
       <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v>510</v>
+        <v>810</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v>930</v>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
+        <v>630</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B12" s="14">
+        <v>400</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="14">
+        <v>150</v>
+      </c>
+      <c r="E12" s="14">
+        <v>150</v>
+      </c>
+      <c r="F12" s="14">
+        <v>200</v>
+      </c>
+      <c r="G12" s="14">
+        <v>4</v>
+      </c>
+      <c r="H12" s="14">
+        <v>250</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+        <v>290</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B13" s="14">
+        <v>420</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="14">
+        <v>90</v>
+      </c>
+      <c r="E13" s="14">
+        <v>90</v>
+      </c>
+      <c r="F13" s="14">
+        <v>350</v>
+      </c>
+      <c r="G13" s="14">
+        <v>7</v>
+      </c>
+      <c r="H13" s="14">
+        <v>200</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
+      <c r="A14" s="13">
+        <v>46260</v>
+      </c>
       <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="C14" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="14">
+        <v>100</v>
+      </c>
+      <c r="E14" s="14">
+        <v>120</v>
+      </c>
+      <c r="F14" s="14">
+        <v>350</v>
+      </c>
+      <c r="G14" s="14">
+        <v>7</v>
+      </c>
+      <c r="H14" s="14">
+        <v>220</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>790</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>650</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
+      <c r="A15" s="13">
+        <v>46261</v>
+      </c>
       <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="C15" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="14">
+        <v>120</v>
+      </c>
+      <c r="E15" s="14">
+        <v>0</v>
+      </c>
+      <c r="F15" s="14">
+        <v>200</v>
+      </c>
+      <c r="G15" s="14">
+        <v>4</v>
+      </c>
+      <c r="H15" s="14">
+        <v>300</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>620</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>820</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
+      <c r="A16" s="13">
+        <v>46262</v>
+      </c>
       <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="C16" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="14">
+        <v>120</v>
+      </c>
+      <c r="E16" s="14">
+        <v>0</v>
+      </c>
+      <c r="F16" s="14">
+        <v>150</v>
+      </c>
+      <c r="G16" s="14">
+        <v>3</v>
+      </c>
+      <c r="H16" s="14">
+        <v>350</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>620</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>820</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
+      <c r="A17" s="13">
+        <v>46263</v>
+      </c>
       <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
+      <c r="C17" s="14" t="s">
+        <v>55</v>
+      </c>
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
       <c r="F17" s="14"/>
@@ -1411,9 +1541,13 @@
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
+      <c r="A18" s="13">
+        <v>46264</v>
+      </c>
       <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
+      <c r="C18" s="14" t="s">
+        <v>55</v>
+      </c>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="14"/>

--- a/12624865.xlsx
+++ b/12624865.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\GIT_DEMO\CAP-776\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1DC871B-5CD1-4D7F-B680-063919809035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1ED04AE-2CDE-4ABA-8C09-AE92A2862532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -233,6 +233,18 @@
   </si>
   <si>
     <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>day was full of lessons!</t>
+  </si>
+  <si>
+    <t>spend time with friends!!</t>
+  </si>
+  <si>
+    <t>learning skills!!</t>
+  </si>
+  <si>
+    <t>focused on skills!!</t>
   </si>
 </sst>
 </file>
@@ -1386,7 +1398,9 @@
       <c r="A14" s="13">
         <v>46260</v>
       </c>
-      <c r="B14" s="14"/>
+      <c r="B14" s="14">
+        <v>420</v>
+      </c>
       <c r="C14" s="14" t="s">
         <v>55</v>
       </c>
@@ -1407,11 +1421,11 @@
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>790</v>
+        <v>1210</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>650</v>
+        <v>230</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>57</v>
@@ -1430,7 +1444,9 @@
       <c r="A15" s="13">
         <v>46261</v>
       </c>
-      <c r="B15" s="14"/>
+      <c r="B15" s="14">
+        <v>420</v>
+      </c>
       <c r="C15" s="14" t="s">
         <v>55</v>
       </c>
@@ -1451,11 +1467,11 @@
       </c>
       <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v>620</v>
+        <v>1040</v>
       </c>
       <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v>820</v>
+        <v>400</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>49</v>
@@ -1474,7 +1490,9 @@
       <c r="A16" s="13">
         <v>46262</v>
       </c>
-      <c r="B16" s="14"/>
+      <c r="B16" s="14">
+        <v>420</v>
+      </c>
       <c r="C16" s="14" t="s">
         <v>55</v>
       </c>
@@ -1495,11 +1513,11 @@
       </c>
       <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v>620</v>
+        <v>1040</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v>820</v>
+        <v>400</v>
       </c>
       <c r="K16" s="16" t="s">
         <v>49</v>
@@ -1518,124 +1536,240 @@
       <c r="A17" s="13">
         <v>46263</v>
       </c>
-      <c r="B17" s="14"/>
+      <c r="B17" s="14">
+        <v>420</v>
+      </c>
       <c r="C17" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="D17" s="14">
+        <v>120</v>
+      </c>
+      <c r="E17" s="14">
+        <v>150</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>350</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
         <v>46264</v>
       </c>
-      <c r="B18" s="14"/>
+      <c r="B18" s="14">
+        <v>420</v>
+      </c>
       <c r="C18" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="D18" s="14">
+        <v>0</v>
+      </c>
+      <c r="E18" s="14">
+        <v>0</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>450</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B19" s="14">
+        <v>400</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="14">
+        <v>120</v>
+      </c>
+      <c r="E19" s="14">
+        <v>60</v>
+      </c>
+      <c r="F19" s="14">
+        <v>200</v>
+      </c>
+      <c r="G19" s="14">
+        <v>4</v>
+      </c>
+      <c r="H19" s="14">
+        <v>250</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B20" s="14">
+        <v>420</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="14">
+        <v>150</v>
+      </c>
+      <c r="E20" s="14">
+        <v>90</v>
+      </c>
+      <c r="F20" s="14">
+        <v>350</v>
+      </c>
+      <c r="G20" s="14">
+        <v>7</v>
+      </c>
+      <c r="H20" s="14">
+        <v>250</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>180</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="14">
+        <v>120</v>
+      </c>
+      <c r="E21" s="14">
+        <v>80</v>
+      </c>
+      <c r="F21" s="14">
+        <v>350</v>
+      </c>
+      <c r="G21" s="14">
+        <v>7</v>
+      </c>
+      <c r="H21" s="14">
+        <v>250</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>220</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
+      <c r="A22" s="13">
+        <v>46268</v>
+      </c>
       <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
+      <c r="C22" s="14" t="s">
+        <v>55</v>
+      </c>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="14"/>
@@ -1655,9 +1789,13 @@
       <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
+      <c r="A23" s="13">
+        <v>46269</v>
+      </c>
       <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
+      <c r="C23" s="14" t="s">
+        <v>55</v>
+      </c>
       <c r="D23" s="14"/>
       <c r="E23" s="14"/>
       <c r="F23" s="14"/>
@@ -1677,9 +1815,13 @@
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
+      <c r="A24" s="13">
+        <v>46270</v>
+      </c>
       <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
+      <c r="C24" s="14" t="s">
+        <v>55</v>
+      </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="14"/>
@@ -1699,9 +1841,13 @@
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
+      <c r="A25" s="13">
+        <v>46271</v>
+      </c>
       <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
+      <c r="C25" s="14" t="s">
+        <v>55</v>
+      </c>
       <c r="D25" s="14"/>
       <c r="E25" s="14"/>
       <c r="F25" s="14"/>
@@ -1721,9 +1867,13 @@
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
+      <c r="A26" s="13">
+        <v>46272</v>
+      </c>
       <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
+      <c r="C26" s="14" t="s">
+        <v>55</v>
+      </c>
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
       <c r="F26" s="14"/>
@@ -1743,9 +1893,13 @@
       <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
+      <c r="A27" s="13">
+        <v>46273</v>
+      </c>
       <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
+      <c r="C27" s="14" t="s">
+        <v>55</v>
+      </c>
       <c r="D27" s="14"/>
       <c r="E27" s="14"/>
       <c r="F27" s="14"/>
@@ -1765,9 +1919,13 @@
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
+      <c r="A28" s="13">
+        <v>46274</v>
+      </c>
       <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
+      <c r="C28" s="14" t="s">
+        <v>55</v>
+      </c>
       <c r="D28" s="14"/>
       <c r="E28" s="14"/>
       <c r="F28" s="14"/>
@@ -1787,9 +1945,13 @@
       <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
+      <c r="A29" s="13">
+        <v>46275</v>
+      </c>
       <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
+      <c r="C29" s="14" t="s">
+        <v>55</v>
+      </c>
       <c r="D29" s="14"/>
       <c r="E29" s="14"/>
       <c r="F29" s="14"/>
@@ -1809,9 +1971,13 @@
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
+      <c r="A30" s="13">
+        <v>46276</v>
+      </c>
       <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
+      <c r="C30" s="14" t="s">
+        <v>55</v>
+      </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
       <c r="F30" s="14"/>

--- a/12624865.xlsx
+++ b/12624865.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\GIT_DEMO\CAP-776\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1ED04AE-2CDE-4ABA-8C09-AE92A2862532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA5204FD-6FF3-4FAE-9E7F-8707D1612193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -245,6 +245,30 @@
   </si>
   <si>
     <t>focused on skills!!</t>
+  </si>
+  <si>
+    <t>spend time in library.</t>
+  </si>
+  <si>
+    <t>felt productive and focused today.</t>
+  </si>
+  <si>
+    <t>had a normal day and focused on learning.</t>
+  </si>
+  <si>
+    <t>had a balanced day with learning and relaxation.</t>
+  </si>
+  <si>
+    <t>learned something new and made good progress.</t>
+  </si>
+  <si>
+    <t>enjoyed the day and complete my important task.</t>
+  </si>
+  <si>
+    <t>had a good day although I felt a little tired.</t>
+  </si>
+  <si>
+    <t>energy was low.</t>
   </si>
 </sst>
 </file>
@@ -1260,7 +1284,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
         <v>46257</v>
       </c>
@@ -1302,9 +1326,11 @@
       <c r="M11" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N11" s="17"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N11" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
         <v>46258</v>
       </c>
@@ -1346,7 +1372,9 @@
       <c r="M12" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N12" s="17"/>
+      <c r="N12" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
@@ -1766,183 +1794,323 @@
       <c r="A22" s="13">
         <v>46268</v>
       </c>
-      <c r="B22" s="14"/>
+      <c r="B22" s="14">
+        <v>400</v>
+      </c>
       <c r="C22" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="D22" s="14">
+        <v>120</v>
+      </c>
+      <c r="E22" s="14">
+        <v>80</v>
+      </c>
+      <c r="F22" s="14">
+        <v>200</v>
+      </c>
+      <c r="G22" s="14">
+        <v>4</v>
+      </c>
+      <c r="H22" s="14">
+        <v>280</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13">
         <v>46269</v>
       </c>
-      <c r="B23" s="14"/>
+      <c r="B23" s="14">
+        <v>420</v>
+      </c>
       <c r="C23" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="D23" s="14">
+        <v>180</v>
+      </c>
+      <c r="E23" s="14">
+        <v>60</v>
+      </c>
+      <c r="F23" s="14">
+        <v>250</v>
+      </c>
+      <c r="G23" s="14">
+        <v>5</v>
+      </c>
+      <c r="H23" s="14">
+        <v>250</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+        <v>280</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="13">
         <v>46270</v>
       </c>
-      <c r="B24" s="14"/>
+      <c r="B24" s="14">
+        <v>360</v>
+      </c>
       <c r="C24" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="D24" s="14">
+        <v>120</v>
+      </c>
+      <c r="E24" s="14">
+        <v>90</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14">
+        <v>320</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+        <v>550</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="13">
         <v>46271</v>
       </c>
-      <c r="B25" s="14"/>
+      <c r="B25" s="14">
+        <v>400</v>
+      </c>
       <c r="C25" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="D25" s="14">
+        <v>150</v>
+      </c>
+      <c r="E25" s="14">
+        <v>60</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>250</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+        <v>580</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="13">
         <v>46272</v>
       </c>
-      <c r="B26" s="14"/>
+      <c r="B26" s="14">
+        <v>360</v>
+      </c>
       <c r="C26" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="D26" s="14">
+        <v>120</v>
+      </c>
+      <c r="E26" s="14">
+        <v>60</v>
+      </c>
+      <c r="F26" s="14">
+        <v>200</v>
+      </c>
+      <c r="G26" s="14">
+        <v>4</v>
+      </c>
+      <c r="H26" s="14">
+        <v>320</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+        <v>380</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="13">
         <v>46273</v>
       </c>
-      <c r="B27" s="14"/>
+      <c r="B27" s="14">
+        <v>320</v>
+      </c>
       <c r="C27" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="D27" s="14">
+        <v>180</v>
+      </c>
+      <c r="E27" s="14">
+        <v>40</v>
+      </c>
+      <c r="F27" s="14">
+        <v>350</v>
+      </c>
+      <c r="G27" s="14">
+        <v>7</v>
+      </c>
+      <c r="H27" s="14">
+        <v>300</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>250</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13">
         <v>46274</v>
       </c>
-      <c r="B28" s="14"/>
+      <c r="B28" s="14">
+        <v>360</v>
+      </c>
       <c r="C28" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="D28" s="14">
+        <v>160</v>
+      </c>
+      <c r="E28" s="14">
+        <v>60</v>
+      </c>
+      <c r="F28" s="14">
+        <v>350</v>
+      </c>
+      <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="14">
+        <v>320</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>190</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13">

--- a/12624865.xlsx
+++ b/12624865.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\GIT_DEMO\CAP-776\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA5204FD-6FF3-4FAE-9E7F-8707D1612193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DCEFB11-1BFE-4BC3-8290-A43C93AB6102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -269,6 +269,12 @@
   </si>
   <si>
     <t>energy was low.</t>
+  </si>
+  <si>
+    <t>had a good day with friends enjoyed freshers partyyy.</t>
+  </si>
+  <si>
+    <t>productive and peacefull day.</t>
   </si>
 </sst>
 </file>
@@ -2112,57 +2118,97 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="13">
         <v>46275</v>
       </c>
-      <c r="B29" s="14"/>
+      <c r="B29" s="14">
+        <v>380</v>
+      </c>
       <c r="C29" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="D29" s="14">
+        <v>120</v>
+      </c>
+      <c r="E29" s="14">
+        <v>90</v>
+      </c>
+      <c r="F29" s="14">
+        <v>200</v>
+      </c>
+      <c r="G29" s="14">
+        <v>4</v>
+      </c>
+      <c r="H29" s="14">
+        <v>320</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>330</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13">
         <v>46276</v>
       </c>
-      <c r="B30" s="14"/>
+      <c r="B30" s="14">
+        <v>420</v>
+      </c>
       <c r="C30" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="D30" s="14">
+        <v>150</v>
+      </c>
+      <c r="E30" s="14">
+        <v>60</v>
+      </c>
+      <c r="F30" s="14">
+        <v>250</v>
+      </c>
+      <c r="G30" s="14">
+        <v>5</v>
+      </c>
+      <c r="H30" s="14">
+        <v>280</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>280</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>

--- a/12624865.xlsx
+++ b/12624865.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\GIT_DEMO\CAP-776\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DCEFB11-1BFE-4BC3-8290-A43C93AB6102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C21C9E-AE5C-4310-BCAB-551953424D9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t>productive and peacefull day.</t>
+  </si>
+  <si>
+    <t>enjoyed the day with friends.</t>
   </si>
 </sst>
 </file>
@@ -2211,109 +2214,211 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B31" s="14">
+        <v>380</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="14">
+        <v>120</v>
+      </c>
+      <c r="E31" s="14">
+        <v>80</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>250</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>610</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B32" s="14">
+        <v>400</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="14">
+        <v>140</v>
+      </c>
+      <c r="E32" s="14">
+        <v>60</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>300</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+        <v>540</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B33" s="14">
+        <v>390</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" s="14">
+        <v>110</v>
+      </c>
+      <c r="E33" s="14">
+        <v>70</v>
+      </c>
+      <c r="F33" s="14">
+        <v>200</v>
+      </c>
+      <c r="G33" s="14">
+        <v>4</v>
+      </c>
+      <c r="H33" s="14">
+        <v>260</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+        <v>410</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B34" s="14">
+        <v>400</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" s="14">
+        <v>120</v>
+      </c>
+      <c r="E34" s="14">
+        <v>60</v>
+      </c>
+      <c r="F34" s="14">
+        <v>350</v>
+      </c>
+      <c r="G34" s="14">
+        <v>7</v>
+      </c>
+      <c r="H34" s="14">
+        <v>300</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>210</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
+      <c r="A35" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B35" s="14">
+        <v>380</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>55</v>
+      </c>
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
       <c r="F35" s="14"/>
       <c r="G35" s="14"/>
       <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>380</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1060</v>
       </c>
       <c r="K35" s="16"/>
       <c r="L35" s="16"/>
@@ -2321,9 +2426,13 @@
       <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
+      <c r="A36" s="13">
+        <v>46282</v>
+      </c>
       <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
+      <c r="C36" s="14" t="s">
+        <v>55</v>
+      </c>
       <c r="D36" s="14"/>
       <c r="E36" s="14"/>
       <c r="F36" s="14"/>
@@ -2343,9 +2452,13 @@
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
+      <c r="A37" s="13">
+        <v>46283</v>
+      </c>
       <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
+      <c r="C37" s="14" t="s">
+        <v>55</v>
+      </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="14"/>
@@ -2365,9 +2478,13 @@
       <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
+      <c r="A38" s="13">
+        <v>46284</v>
+      </c>
       <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
+      <c r="C38" s="14" t="s">
+        <v>55</v>
+      </c>
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
       <c r="F38" s="14"/>
@@ -2387,9 +2504,13 @@
       <c r="N38" s="17"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
+      <c r="A39" s="13">
+        <v>46285</v>
+      </c>
       <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
+      <c r="C39" s="14" t="s">
+        <v>55</v>
+      </c>
       <c r="D39" s="14"/>
       <c r="E39" s="14"/>
       <c r="F39" s="14"/>
@@ -2409,9 +2530,13 @@
       <c r="N39" s="17"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
+      <c r="A40" s="13">
+        <v>46286</v>
+      </c>
       <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
+      <c r="C40" s="14" t="s">
+        <v>55</v>
+      </c>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="14"/>

--- a/12624865.xlsx
+++ b/12624865.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\GIT_DEMO\CAP-776\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C21C9E-AE5C-4310-BCAB-551953424D9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F8CEEA6-3CBF-4077-81CC-F3B682E43FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -278,6 +279,24 @@
   </si>
   <si>
     <t>enjoyed the day with friends.</t>
+  </si>
+  <si>
+    <t>Studing with full focus and dedication.</t>
+  </si>
+  <si>
+    <t>Celebrate friend's birthday!!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Give analitics CA. </t>
+  </si>
+  <si>
+    <t>felt tierd and sleepyy!!</t>
+  </si>
+  <si>
+    <t>had a good day.</t>
+  </si>
+  <si>
+    <t>learned something and devloped new skills!!</t>
   </si>
 </sst>
 </file>
@@ -2407,153 +2426,271 @@
       <c r="C35" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
+      <c r="D35" s="14">
+        <v>220</v>
+      </c>
+      <c r="E35" s="14">
+        <v>60</v>
+      </c>
+      <c r="F35" s="14">
+        <v>350</v>
+      </c>
+      <c r="G35" s="14">
+        <v>7</v>
+      </c>
+      <c r="H35" s="14">
+        <v>250</v>
+      </c>
       <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v>380</v>
+        <v>1260</v>
       </c>
       <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v>1060</v>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>180</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13">
         <v>46282</v>
       </c>
-      <c r="B36" s="14"/>
+      <c r="B36" s="14">
+        <v>360</v>
+      </c>
       <c r="C36" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="D36" s="14">
+        <v>160</v>
+      </c>
+      <c r="E36" s="14">
+        <v>80</v>
+      </c>
+      <c r="F36" s="14">
+        <v>200</v>
+      </c>
+      <c r="G36" s="14">
+        <v>4</v>
+      </c>
+      <c r="H36" s="14">
+        <v>280</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+        <v>360</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="13">
         <v>46283</v>
       </c>
-      <c r="B37" s="14"/>
+      <c r="B37" s="14">
+        <v>400</v>
+      </c>
       <c r="C37" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="D37" s="14">
+        <v>180</v>
+      </c>
+      <c r="E37" s="14">
+        <v>40</v>
+      </c>
+      <c r="F37" s="14">
+        <v>250</v>
+      </c>
+      <c r="G37" s="14">
+        <v>5</v>
+      </c>
+      <c r="H37" s="14">
+        <v>320</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>250</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="13">
         <v>46284</v>
       </c>
-      <c r="B38" s="14"/>
+      <c r="B38" s="14">
+        <v>380</v>
+      </c>
       <c r="C38" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="D38" s="14">
+        <v>180</v>
+      </c>
+      <c r="E38" s="14">
+        <v>60</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>340</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+        <v>480</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="13">
         <v>46285</v>
       </c>
-      <c r="B39" s="14"/>
+      <c r="B39" s="14">
+        <v>400</v>
+      </c>
       <c r="C39" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="D39" s="14">
+        <v>300</v>
+      </c>
+      <c r="E39" s="14">
+        <v>120</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>260</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="13">
         <v>46286</v>
       </c>
-      <c r="B40" s="14"/>
+      <c r="B40" s="14">
+        <v>380</v>
+      </c>
       <c r="C40" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="D40" s="14">
+        <v>220</v>
+      </c>
+      <c r="E40" s="14">
+        <v>60</v>
+      </c>
+      <c r="F40" s="14">
+        <v>200</v>
+      </c>
+      <c r="G40" s="14">
+        <v>4</v>
+      </c>
+      <c r="H40" s="14">
+        <v>350</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>230</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>

--- a/12624865.xlsx
+++ b/12624865.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\GIT_DEMO\CAP-776\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C25791A3-37D7-40EA-B7E3-B0EF6874A7CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89BCABFA-5A86-4C96-8E46-6F8B12082BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -302,6 +302,42 @@
   </si>
   <si>
     <t>feeling tired todayy!!</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Enjoyed time with friends.</t>
+  </si>
+  <si>
+    <t>Attended extra classes</t>
+  </si>
+  <si>
+    <t>A protest was held at our university.</t>
+  </si>
+  <si>
+    <t>University gave us 10 days of holidays.</t>
+  </si>
+  <si>
+    <t>Going back home.</t>
+  </si>
+  <si>
+    <t>Reached home.</t>
+  </si>
+  <si>
+    <t>Spent time with family.</t>
+  </si>
+  <si>
+    <t>Met my old friends.</t>
+  </si>
+  <si>
+    <t>Attended my friend's baraat.</t>
+  </si>
+  <si>
+    <t>Attended my friend's wedding functions.</t>
   </si>
 </sst>
 </file>
@@ -2834,264 +2870,516 @@
       <c r="A44" s="12">
         <v>46289</v>
       </c>
-      <c r="B44" s="13"/>
+      <c r="B44" s="13">
+        <v>360</v>
+      </c>
       <c r="C44" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="14" t="str">
+      <c r="D44" s="13">
+        <v>180</v>
+      </c>
+      <c r="E44" s="13">
+        <v>60</v>
+      </c>
+      <c r="F44" s="13">
+        <v>200</v>
+      </c>
+      <c r="G44" s="13">
+        <v>4</v>
+      </c>
+      <c r="H44" s="13">
+        <v>320</v>
+      </c>
+      <c r="I44" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="14" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J44" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="15"/>
-      <c r="L44" s="15"/>
-      <c r="M44" s="15"/>
-      <c r="N44" s="16"/>
+        <v>320</v>
+      </c>
+      <c r="K44" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="M44" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" s="16" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="12">
         <v>46290</v>
       </c>
-      <c r="B45" s="13"/>
+      <c r="B45" s="13">
+        <v>350</v>
+      </c>
       <c r="C45" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="14" t="str">
+      <c r="D45" s="13">
+        <v>160</v>
+      </c>
+      <c r="E45" s="13">
+        <v>40</v>
+      </c>
+      <c r="F45" s="13">
+        <v>250</v>
+      </c>
+      <c r="G45" s="13">
+        <v>5</v>
+      </c>
+      <c r="H45" s="13">
+        <v>360</v>
+      </c>
+      <c r="I45" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="14" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J45" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="15"/>
-      <c r="L45" s="15"/>
-      <c r="M45" s="15"/>
-      <c r="N45" s="16"/>
+        <v>280</v>
+      </c>
+      <c r="K45" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="L45" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="M45" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" s="16" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="12">
         <v>46291</v>
       </c>
-      <c r="B46" s="13"/>
+      <c r="B46" s="13">
+        <v>380</v>
+      </c>
       <c r="C46" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="14" t="str">
+      <c r="D46" s="13">
+        <v>160</v>
+      </c>
+      <c r="E46" s="13">
+        <v>80</v>
+      </c>
+      <c r="F46" s="13">
+        <v>150</v>
+      </c>
+      <c r="G46" s="13">
+        <v>3</v>
+      </c>
+      <c r="H46" s="13">
+        <v>390</v>
+      </c>
+      <c r="I46" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="14" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J46" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="15"/>
-      <c r="L46" s="15"/>
-      <c r="M46" s="15"/>
-      <c r="N46" s="16"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+        <v>280</v>
+      </c>
+      <c r="K46" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="L46" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="M46" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N46" s="16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="12">
         <v>46292</v>
       </c>
-      <c r="B47" s="13"/>
+      <c r="B47" s="13">
+        <v>400</v>
+      </c>
       <c r="C47" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="14" t="str">
+      <c r="D47" s="13">
+        <v>140</v>
+      </c>
+      <c r="E47" s="13">
+        <v>40</v>
+      </c>
+      <c r="F47" s="13">
+        <v>0</v>
+      </c>
+      <c r="G47" s="13">
+        <v>0</v>
+      </c>
+      <c r="H47" s="13">
+        <v>360</v>
+      </c>
+      <c r="I47" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="14" t="str">
+        <v>940</v>
+      </c>
+      <c r="J47" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="15"/>
-      <c r="L47" s="15"/>
-      <c r="M47" s="15"/>
-      <c r="N47" s="16"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="12"/>
-      <c r="B48" s="13"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="14" t="str">
+        <v>500</v>
+      </c>
+      <c r="K47" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L47" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M47" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N47" s="16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="12">
+        <v>46293</v>
+      </c>
+      <c r="B48" s="13">
+        <v>420</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D48" s="13">
+        <v>120</v>
+      </c>
+      <c r="E48" s="13">
+        <v>60</v>
+      </c>
+      <c r="F48" s="13">
+        <v>0</v>
+      </c>
+      <c r="G48" s="13">
+        <v>0</v>
+      </c>
+      <c r="H48" s="13">
+        <v>380</v>
+      </c>
+      <c r="I48" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="14" t="str">
+        <v>980</v>
+      </c>
+      <c r="J48" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="15"/>
-      <c r="L48" s="15"/>
-      <c r="M48" s="15"/>
-      <c r="N48" s="16"/>
+        <v>460</v>
+      </c>
+      <c r="K48" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="L48" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="M48" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N48" s="16" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="12"/>
-      <c r="B49" s="13"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="13"/>
-      <c r="I49" s="14" t="str">
+      <c r="A49" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B49" s="13">
+        <v>320</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D49" s="13">
+        <v>90</v>
+      </c>
+      <c r="E49" s="13">
+        <v>50</v>
+      </c>
+      <c r="F49" s="13">
+        <v>0</v>
+      </c>
+      <c r="G49" s="13">
+        <v>0</v>
+      </c>
+      <c r="H49" s="13">
+        <v>320</v>
+      </c>
+      <c r="I49" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="14" t="str">
+        <v>780</v>
+      </c>
+      <c r="J49" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="15"/>
-      <c r="L49" s="15"/>
-      <c r="M49" s="15"/>
-      <c r="N49" s="16"/>
+        <v>660</v>
+      </c>
+      <c r="K49" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="L49" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="M49" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N49" s="16" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="12"/>
-      <c r="B50" s="13"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="14" t="str">
+      <c r="A50" s="12">
+        <v>46295</v>
+      </c>
+      <c r="B50" s="13">
+        <v>330</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D50" s="13">
+        <v>120</v>
+      </c>
+      <c r="E50" s="13">
+        <v>80</v>
+      </c>
+      <c r="F50" s="13">
+        <v>0</v>
+      </c>
+      <c r="G50" s="13">
+        <v>0</v>
+      </c>
+      <c r="H50" s="13">
+        <v>300</v>
+      </c>
+      <c r="I50" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="14" t="str">
+        <v>830</v>
+      </c>
+      <c r="J50" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="15"/>
-      <c r="L50" s="15"/>
-      <c r="M50" s="15"/>
-      <c r="N50" s="16"/>
+        <v>610</v>
+      </c>
+      <c r="K50" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L50" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M50" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N50" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="12"/>
-      <c r="B51" s="13"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="14" t="str">
+      <c r="A51" s="12">
+        <v>46296</v>
+      </c>
+      <c r="B51" s="13">
+        <v>380</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D51" s="13">
+        <v>60</v>
+      </c>
+      <c r="E51" s="13">
+        <v>70</v>
+      </c>
+      <c r="F51" s="13">
+        <v>0</v>
+      </c>
+      <c r="G51" s="13">
+        <v>0</v>
+      </c>
+      <c r="H51" s="13">
+        <v>280</v>
+      </c>
+      <c r="I51" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="14" t="str">
+        <v>790</v>
+      </c>
+      <c r="J51" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="15"/>
-      <c r="L51" s="15"/>
-      <c r="M51" s="15"/>
-      <c r="N51" s="16"/>
+        <v>650</v>
+      </c>
+      <c r="K51" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="L51" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="M51" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N51" s="16" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="12"/>
-      <c r="B52" s="13"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
-      <c r="I52" s="14" t="str">
+      <c r="A52" s="12">
+        <v>46297</v>
+      </c>
+      <c r="B52" s="13">
+        <v>390</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D52" s="13">
+        <v>80</v>
+      </c>
+      <c r="E52" s="13">
+        <v>50</v>
+      </c>
+      <c r="F52" s="13">
+        <v>0</v>
+      </c>
+      <c r="G52" s="13">
+        <v>0</v>
+      </c>
+      <c r="H52" s="13">
+        <v>260</v>
+      </c>
+      <c r="I52" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="14" t="str">
+        <v>780</v>
+      </c>
+      <c r="J52" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="15"/>
-      <c r="L52" s="15"/>
-      <c r="M52" s="15"/>
-      <c r="N52" s="16"/>
+        <v>660</v>
+      </c>
+      <c r="K52" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L52" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M52" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N52" s="16" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="12"/>
-      <c r="B53" s="13"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="13"/>
-      <c r="I53" s="14" t="str">
+      <c r="A53" s="12">
+        <v>46298</v>
+      </c>
+      <c r="B53" s="13">
+        <v>390</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D53" s="13">
+        <v>110</v>
+      </c>
+      <c r="E53" s="13">
+        <v>40</v>
+      </c>
+      <c r="F53" s="13">
+        <v>0</v>
+      </c>
+      <c r="G53" s="13">
+        <v>0</v>
+      </c>
+      <c r="H53" s="13">
+        <v>420</v>
+      </c>
+      <c r="I53" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="14" t="str">
+        <v>960</v>
+      </c>
+      <c r="J53" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="15"/>
-      <c r="L53" s="15"/>
-      <c r="M53" s="15"/>
-      <c r="N53" s="16"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="12"/>
-      <c r="B54" s="13"/>
-      <c r="C54" s="13"/>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
-      <c r="I54" s="14" t="str">
+        <v>480</v>
+      </c>
+      <c r="K53" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="L53" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="M53" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N53" s="16" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="12">
+        <v>46299</v>
+      </c>
+      <c r="B54" s="13">
+        <v>340</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D54" s="13">
+        <v>140</v>
+      </c>
+      <c r="E54" s="13">
+        <v>60</v>
+      </c>
+      <c r="F54" s="13">
+        <v>0</v>
+      </c>
+      <c r="G54" s="13">
+        <v>0</v>
+      </c>
+      <c r="H54" s="13">
+        <v>400</v>
+      </c>
+      <c r="I54" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="14" t="str">
+        <v>940</v>
+      </c>
+      <c r="J54" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="15"/>
-      <c r="L54" s="15"/>
-      <c r="M54" s="15"/>
-      <c r="N54" s="16"/>
+        <v>500</v>
+      </c>
+      <c r="K54" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="L54" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="M54" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N54" s="16" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="12"/>
+      <c r="A55" s="12">
+        <v>46300</v>
+      </c>
       <c r="B55" s="13"/>
-      <c r="C55" s="13"/>
+      <c r="C55" s="13" t="s">
+        <v>55</v>
+      </c>
       <c r="D55" s="13"/>
       <c r="E55" s="13"/>
       <c r="F55" s="13"/>

--- a/12624865.xlsx
+++ b/12624865.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\GIT_DEMO\CAP-776\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89BCABFA-5A86-4C96-8E46-6F8B12082BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A4500F-CE5D-44FB-BE89-982A41294171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="109">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -202,9 +202,6 @@
     <t xml:space="preserve">MCA </t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
     <t>Neutral</t>
   </si>
   <si>
@@ -338,6 +335,33 @@
   </si>
   <si>
     <t>Attended my friend's wedding functions.</t>
+  </si>
+  <si>
+    <t>Attended online classes.</t>
+  </si>
+  <si>
+    <t>Going back university.</t>
+  </si>
+  <si>
+    <t>Reached university.</t>
+  </si>
+  <si>
+    <t>Mid-Term was started.</t>
+  </si>
+  <si>
+    <t>Give 3 MT.</t>
+  </si>
+  <si>
+    <t>Give 2 MT.</t>
+  </si>
+  <si>
+    <t>Give 4 MT.</t>
+  </si>
+  <si>
+    <t>Give 5 MT.</t>
+  </si>
+  <si>
+    <t>Give last MT.</t>
   </si>
 </sst>
 </file>
@@ -1054,7 +1078,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G3" s="19"/>
     </row>
@@ -1127,8 +1151,8 @@
       <c r="B6" s="8">
         <v>420</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>55</v>
+      <c r="C6" s="8">
+        <v>0</v>
       </c>
       <c r="D6" s="8">
         <v>120</v>
@@ -1154,16 +1178,16 @@
         <v>310</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L6" s="10" t="s">
         <v>50</v>
       </c>
       <c r="M6" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="N6" s="11" t="s">
         <v>57</v>
-      </c>
-      <c r="N6" s="11" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1173,8 +1197,8 @@
       <c r="B7" s="8">
         <v>420</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>55</v>
+      <c r="C7" s="8">
+        <v>0</v>
       </c>
       <c r="D7" s="8">
         <v>120</v>
@@ -1198,16 +1222,16 @@
         <v>340</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>51</v>
       </c>
       <c r="N7" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1217,8 +1241,8 @@
       <c r="B8" s="13">
         <v>420</v>
       </c>
-      <c r="C8" s="13" t="s">
-        <v>55</v>
+      <c r="C8" s="13">
+        <v>0</v>
       </c>
       <c r="D8" s="13">
         <v>120</v>
@@ -1253,7 +1277,7 @@
         <v>51</v>
       </c>
       <c r="N8" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1263,8 +1287,8 @@
       <c r="B9" s="13">
         <v>420</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>55</v>
+      <c r="C9" s="13">
+        <v>0</v>
       </c>
       <c r="D9" s="13">
         <v>0</v>
@@ -1296,10 +1320,10 @@
         <v>50</v>
       </c>
       <c r="M9" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="N9" s="16" t="s">
         <v>61</v>
-      </c>
-      <c r="N9" s="16" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1309,8 +1333,8 @@
       <c r="B10" s="13">
         <v>420</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>55</v>
+      <c r="C10" s="13">
+        <v>20</v>
       </c>
       <c r="D10" s="13">
         <v>120</v>
@@ -1329,23 +1353,23 @@
       </c>
       <c r="I10" s="14">
         <f t="shared" si="0"/>
-        <v>1120</v>
+        <v>1140</v>
       </c>
       <c r="J10" s="14">
         <f t="shared" si="1"/>
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>49</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M10" s="15" t="s">
         <v>51</v>
       </c>
       <c r="N10" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1355,8 +1379,8 @@
       <c r="B11" s="13">
         <v>400</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>55</v>
+      <c r="C11" s="13">
+        <v>0</v>
       </c>
       <c r="D11" s="13">
         <v>100</v>
@@ -1391,7 +1415,7 @@
         <v>51</v>
       </c>
       <c r="N11" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1401,8 +1425,8 @@
       <c r="B12" s="13">
         <v>360</v>
       </c>
-      <c r="C12" s="13" t="s">
-        <v>55</v>
+      <c r="C12" s="13">
+        <v>25</v>
       </c>
       <c r="D12" s="13">
         <v>0</v>
@@ -1421,14 +1445,14 @@
       </c>
       <c r="I12" s="14">
         <f t="shared" si="0"/>
-        <v>810</v>
+        <v>835</v>
       </c>
       <c r="J12" s="14">
         <f t="shared" si="1"/>
-        <v>630</v>
+        <v>605</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L12" s="15" t="s">
         <v>50</v>
@@ -1437,7 +1461,7 @@
         <v>51</v>
       </c>
       <c r="N12" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1447,8 +1471,8 @@
       <c r="B13" s="13">
         <v>400</v>
       </c>
-      <c r="C13" s="13" t="s">
-        <v>55</v>
+      <c r="C13" s="13">
+        <v>0</v>
       </c>
       <c r="D13" s="13">
         <v>150</v>
@@ -1474,16 +1498,16 @@
         <v>290</v>
       </c>
       <c r="K13" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M13" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="L13" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="M13" s="15" t="s">
-        <v>57</v>
-      </c>
       <c r="N13" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1493,8 +1517,8 @@
       <c r="B14" s="13">
         <v>420</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>55</v>
+      <c r="C14" s="13">
+        <v>0</v>
       </c>
       <c r="D14" s="13">
         <v>90</v>
@@ -1520,16 +1544,16 @@
         <v>290</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L14" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M14" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="M14" s="15" t="s">
-        <v>57</v>
-      </c>
       <c r="N14" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1539,8 +1563,8 @@
       <c r="B15" s="13">
         <v>420</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>55</v>
+      <c r="C15" s="13">
+        <v>0</v>
       </c>
       <c r="D15" s="13">
         <v>100</v>
@@ -1566,16 +1590,16 @@
         <v>230</v>
       </c>
       <c r="K15" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="M15" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="N15" s="16" t="s">
         <v>57</v>
-      </c>
-      <c r="L15" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="M15" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="N15" s="16" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1585,8 +1609,8 @@
       <c r="B16" s="13">
         <v>420</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>55</v>
+      <c r="C16" s="13">
+        <v>0</v>
       </c>
       <c r="D16" s="13">
         <v>120</v>
@@ -1621,7 +1645,7 @@
         <v>51</v>
       </c>
       <c r="N16" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1631,8 +1655,8 @@
       <c r="B17" s="13">
         <v>420</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>55</v>
+      <c r="C17" s="13">
+        <v>0</v>
       </c>
       <c r="D17" s="13">
         <v>120</v>
@@ -1664,10 +1688,10 @@
         <v>50</v>
       </c>
       <c r="M17" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="N17" s="16" t="s">
         <v>61</v>
-      </c>
-      <c r="N17" s="16" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1677,8 +1701,8 @@
       <c r="B18" s="13">
         <v>420</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>55</v>
+      <c r="C18" s="13">
+        <v>0</v>
       </c>
       <c r="D18" s="13">
         <v>120</v>
@@ -1707,13 +1731,13 @@
         <v>49</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M18" s="15" t="s">
         <v>51</v>
       </c>
       <c r="N18" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1723,8 +1747,8 @@
       <c r="B19" s="13">
         <v>420</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>55</v>
+      <c r="C19" s="13">
+        <v>0</v>
       </c>
       <c r="D19" s="13">
         <v>0</v>
@@ -1759,7 +1783,7 @@
         <v>51</v>
       </c>
       <c r="N19" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1769,8 +1793,8 @@
       <c r="B20" s="13">
         <v>400</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>55</v>
+      <c r="C20" s="13">
+        <v>0</v>
       </c>
       <c r="D20" s="13">
         <v>120</v>
@@ -1796,16 +1820,16 @@
         <v>410</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M20" s="15" t="s">
         <v>51</v>
       </c>
       <c r="N20" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -1815,8 +1839,8 @@
       <c r="B21" s="13">
         <v>420</v>
       </c>
-      <c r="C21" s="13" t="s">
-        <v>55</v>
+      <c r="C21" s="13">
+        <v>0</v>
       </c>
       <c r="D21" s="13">
         <v>150</v>
@@ -1842,16 +1866,16 @@
         <v>180</v>
       </c>
       <c r="K21" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="L21" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M21" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="N21" s="16" t="s">
         <v>57</v>
-      </c>
-      <c r="L21" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="M21" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="N21" s="16" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -1861,8 +1885,8 @@
       <c r="B22" s="13">
         <v>420</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>55</v>
+      <c r="C22" s="13">
+        <v>0</v>
       </c>
       <c r="D22" s="13">
         <v>120</v>
@@ -1888,16 +1912,16 @@
         <v>220</v>
       </c>
       <c r="K22" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="L22" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M22" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="L22" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="M22" s="15" t="s">
-        <v>57</v>
-      </c>
       <c r="N22" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -1907,8 +1931,8 @@
       <c r="B23" s="13">
         <v>400</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>55</v>
+      <c r="C23" s="13">
+        <v>0</v>
       </c>
       <c r="D23" s="13">
         <v>120</v>
@@ -1934,7 +1958,7 @@
         <v>360</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L23" s="15" t="s">
         <v>50</v>
@@ -1943,7 +1967,7 @@
         <v>51</v>
       </c>
       <c r="N23" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -1953,8 +1977,8 @@
       <c r="B24" s="13">
         <v>420</v>
       </c>
-      <c r="C24" s="13" t="s">
-        <v>55</v>
+      <c r="C24" s="13">
+        <v>0</v>
       </c>
       <c r="D24" s="13">
         <v>180</v>
@@ -1983,13 +2007,13 @@
         <v>49</v>
       </c>
       <c r="L24" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M24" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="M24" s="15" t="s">
-        <v>57</v>
-      </c>
       <c r="N24" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1999,8 +2023,8 @@
       <c r="B25" s="13">
         <v>360</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>55</v>
+      <c r="C25" s="13">
+        <v>0</v>
       </c>
       <c r="D25" s="13">
         <v>120</v>
@@ -2029,13 +2053,13 @@
         <v>49</v>
       </c>
       <c r="L25" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M25" s="15" t="s">
         <v>51</v>
       </c>
       <c r="N25" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2045,8 +2069,8 @@
       <c r="B26" s="13">
         <v>400</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>55</v>
+      <c r="C26" s="13">
+        <v>0</v>
       </c>
       <c r="D26" s="13">
         <v>150</v>
@@ -2081,7 +2105,7 @@
         <v>51</v>
       </c>
       <c r="N26" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2091,8 +2115,8 @@
       <c r="B27" s="13">
         <v>360</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>55</v>
+      <c r="C27" s="13">
+        <v>0</v>
       </c>
       <c r="D27" s="13">
         <v>120</v>
@@ -2118,16 +2142,16 @@
         <v>380</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L27" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M27" s="15" t="s">
         <v>51</v>
       </c>
       <c r="N27" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2137,8 +2161,8 @@
       <c r="B28" s="13">
         <v>320</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>55</v>
+      <c r="C28" s="13">
+        <v>0</v>
       </c>
       <c r="D28" s="13">
         <v>180</v>
@@ -2167,13 +2191,13 @@
         <v>49</v>
       </c>
       <c r="L28" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M28" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="M28" s="15" t="s">
-        <v>57</v>
-      </c>
       <c r="N28" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -2183,8 +2207,8 @@
       <c r="B29" s="13">
         <v>360</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>55</v>
+      <c r="C29" s="13">
+        <v>0</v>
       </c>
       <c r="D29" s="13">
         <v>160</v>
@@ -2210,16 +2234,16 @@
         <v>190</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L29" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M29" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="M29" s="15" t="s">
-        <v>57</v>
-      </c>
       <c r="N29" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2229,8 +2253,8 @@
       <c r="B30" s="13">
         <v>380</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>55</v>
+      <c r="C30" s="13">
+        <v>0</v>
       </c>
       <c r="D30" s="13">
         <v>120</v>
@@ -2259,13 +2283,13 @@
         <v>49</v>
       </c>
       <c r="L30" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M30" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="M30" s="15" t="s">
-        <v>57</v>
-      </c>
       <c r="N30" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -2275,8 +2299,8 @@
       <c r="B31" s="13">
         <v>420</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>55</v>
+      <c r="C31" s="13">
+        <v>0</v>
       </c>
       <c r="D31" s="13">
         <v>150</v>
@@ -2302,16 +2326,16 @@
         <v>280</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L31" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M31" s="15" t="s">
         <v>51</v>
       </c>
       <c r="N31" s="16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -2321,8 +2345,8 @@
       <c r="B32" s="13">
         <v>380</v>
       </c>
-      <c r="C32" s="13" t="s">
-        <v>55</v>
+      <c r="C32" s="13">
+        <v>60</v>
       </c>
       <c r="D32" s="13">
         <v>120</v>
@@ -2341,23 +2365,23 @@
       </c>
       <c r="I32" s="14">
         <f t="shared" si="0"/>
-        <v>830</v>
+        <v>890</v>
       </c>
       <c r="J32" s="14">
         <f t="shared" si="1"/>
-        <v>610</v>
+        <v>550</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L32" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M32" s="15" t="s">
         <v>51</v>
       </c>
       <c r="N32" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
@@ -2367,8 +2391,8 @@
       <c r="B33" s="13">
         <v>400</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>55</v>
+      <c r="C33" s="13">
+        <v>60</v>
       </c>
       <c r="D33" s="13">
         <v>140</v>
@@ -2387,11 +2411,11 @@
       </c>
       <c r="I33" s="14">
         <f t="shared" si="0"/>
-        <v>900</v>
+        <v>960</v>
       </c>
       <c r="J33" s="14">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>480</v>
       </c>
       <c r="K33" s="15" t="s">
         <v>49</v>
@@ -2403,7 +2427,7 @@
         <v>51</v>
       </c>
       <c r="N33" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2413,8 +2437,8 @@
       <c r="B34" s="13">
         <v>390</v>
       </c>
-      <c r="C34" s="13" t="s">
-        <v>55</v>
+      <c r="C34" s="13">
+        <v>0</v>
       </c>
       <c r="D34" s="13">
         <v>110</v>
@@ -2443,13 +2467,13 @@
         <v>49</v>
       </c>
       <c r="L34" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M34" s="15" t="s">
         <v>51</v>
       </c>
       <c r="N34" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2459,8 +2483,8 @@
       <c r="B35" s="13">
         <v>400</v>
       </c>
-      <c r="C35" s="13" t="s">
-        <v>55</v>
+      <c r="C35" s="13">
+        <v>0</v>
       </c>
       <c r="D35" s="13">
         <v>120</v>
@@ -2486,16 +2510,16 @@
         <v>210</v>
       </c>
       <c r="K35" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L35" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M35" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="M35" s="15" t="s">
-        <v>57</v>
-      </c>
       <c r="N35" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
@@ -2505,8 +2529,8 @@
       <c r="B36" s="13">
         <v>380</v>
       </c>
-      <c r="C36" s="13" t="s">
-        <v>55</v>
+      <c r="C36" s="13">
+        <v>0</v>
       </c>
       <c r="D36" s="13">
         <v>220</v>
@@ -2532,16 +2556,16 @@
         <v>180</v>
       </c>
       <c r="K36" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L36" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M36" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="M36" s="15" t="s">
-        <v>57</v>
-      </c>
       <c r="N36" s="16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
@@ -2551,8 +2575,8 @@
       <c r="B37" s="13">
         <v>360</v>
       </c>
-      <c r="C37" s="13" t="s">
-        <v>55</v>
+      <c r="C37" s="13">
+        <v>0</v>
       </c>
       <c r="D37" s="13">
         <v>160</v>
@@ -2578,7 +2602,7 @@
         <v>360</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L37" s="15" t="s">
         <v>50</v>
@@ -2587,7 +2611,7 @@
         <v>51</v>
       </c>
       <c r="N37" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2597,8 +2621,8 @@
       <c r="B38" s="13">
         <v>400</v>
       </c>
-      <c r="C38" s="13" t="s">
-        <v>55</v>
+      <c r="C38" s="13">
+        <v>0</v>
       </c>
       <c r="D38" s="13">
         <v>180</v>
@@ -2624,7 +2648,7 @@
         <v>250</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L38" s="15" t="s">
         <v>50</v>
@@ -2633,7 +2657,7 @@
         <v>51</v>
       </c>
       <c r="N38" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
@@ -2643,8 +2667,8 @@
       <c r="B39" s="13">
         <v>380</v>
       </c>
-      <c r="C39" s="13" t="s">
-        <v>55</v>
+      <c r="C39" s="13">
+        <v>60</v>
       </c>
       <c r="D39" s="13">
         <v>180</v>
@@ -2663,23 +2687,23 @@
       </c>
       <c r="I39" s="14">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>1020</v>
       </c>
       <c r="J39" s="14">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="K39" s="15" t="s">
         <v>49</v>
       </c>
       <c r="L39" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M39" s="15" t="s">
         <v>51</v>
       </c>
       <c r="N39" s="16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2689,8 +2713,8 @@
       <c r="B40" s="13">
         <v>400</v>
       </c>
-      <c r="C40" s="13" t="s">
-        <v>55</v>
+      <c r="C40" s="13">
+        <v>60</v>
       </c>
       <c r="D40" s="13">
         <v>300</v>
@@ -2709,23 +2733,23 @@
       </c>
       <c r="I40" s="14">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>1140</v>
       </c>
       <c r="J40" s="14">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="K40" s="15" t="s">
         <v>49</v>
       </c>
       <c r="L40" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M40" s="15" t="s">
         <v>51</v>
       </c>
       <c r="N40" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
@@ -2735,8 +2759,8 @@
       <c r="B41" s="13">
         <v>380</v>
       </c>
-      <c r="C41" s="13" t="s">
-        <v>55</v>
+      <c r="C41" s="13">
+        <v>0</v>
       </c>
       <c r="D41" s="13">
         <v>220</v>
@@ -2762,7 +2786,7 @@
         <v>230</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L41" s="15" t="s">
         <v>50</v>
@@ -2771,7 +2795,7 @@
         <v>51</v>
       </c>
       <c r="N41" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
@@ -2781,8 +2805,8 @@
       <c r="B42" s="13">
         <v>380</v>
       </c>
-      <c r="C42" s="13" t="s">
-        <v>55</v>
+      <c r="C42" s="13">
+        <v>0</v>
       </c>
       <c r="D42" s="13">
         <v>120</v>
@@ -2817,7 +2841,7 @@
         <v>51</v>
       </c>
       <c r="N42" s="16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
@@ -2827,8 +2851,8 @@
       <c r="B43" s="13">
         <v>360</v>
       </c>
-      <c r="C43" s="13" t="s">
-        <v>55</v>
+      <c r="C43" s="13">
+        <v>0</v>
       </c>
       <c r="D43" s="13">
         <v>160</v>
@@ -2854,16 +2878,16 @@
         <v>290</v>
       </c>
       <c r="K43" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="L43" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M43" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="L43" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="M43" s="15" t="s">
-        <v>57</v>
-      </c>
       <c r="N43" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
@@ -2873,8 +2897,8 @@
       <c r="B44" s="13">
         <v>360</v>
       </c>
-      <c r="C44" s="13" t="s">
-        <v>55</v>
+      <c r="C44" s="13">
+        <v>0</v>
       </c>
       <c r="D44" s="13">
         <v>180</v>
@@ -2903,13 +2927,13 @@
         <v>49</v>
       </c>
       <c r="L44" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M44" s="15" t="s">
         <v>51</v>
       </c>
       <c r="N44" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
@@ -2919,8 +2943,8 @@
       <c r="B45" s="13">
         <v>350</v>
       </c>
-      <c r="C45" s="13" t="s">
-        <v>55</v>
+      <c r="C45" s="13">
+        <v>0</v>
       </c>
       <c r="D45" s="13">
         <v>160</v>
@@ -2946,16 +2970,16 @@
         <v>280</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L45" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M45" s="15" t="s">
         <v>51</v>
       </c>
       <c r="N45" s="16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
@@ -2965,8 +2989,8 @@
       <c r="B46" s="13">
         <v>380</v>
       </c>
-      <c r="C46" s="13" t="s">
-        <v>55</v>
+      <c r="C46" s="13">
+        <v>0</v>
       </c>
       <c r="D46" s="13">
         <v>160</v>
@@ -2992,16 +3016,16 @@
         <v>280</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L46" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M46" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N46" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -3011,8 +3035,8 @@
       <c r="B47" s="13">
         <v>400</v>
       </c>
-      <c r="C47" s="13" t="s">
-        <v>55</v>
+      <c r="C47" s="13">
+        <v>0</v>
       </c>
       <c r="D47" s="13">
         <v>140</v>
@@ -3044,10 +3068,10 @@
         <v>50</v>
       </c>
       <c r="M47" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N47" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -3057,8 +3081,8 @@
       <c r="B48" s="13">
         <v>420</v>
       </c>
-      <c r="C48" s="13" t="s">
-        <v>55</v>
+      <c r="C48" s="13">
+        <v>0</v>
       </c>
       <c r="D48" s="13">
         <v>120</v>
@@ -3084,16 +3108,16 @@
         <v>460</v>
       </c>
       <c r="K48" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="L48" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="L48" s="15" t="s">
-        <v>90</v>
-      </c>
       <c r="M48" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N48" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
@@ -3103,8 +3127,8 @@
       <c r="B49" s="13">
         <v>320</v>
       </c>
-      <c r="C49" s="13" t="s">
-        <v>55</v>
+      <c r="C49" s="13">
+        <v>0</v>
       </c>
       <c r="D49" s="13">
         <v>90</v>
@@ -3130,16 +3154,16 @@
         <v>660</v>
       </c>
       <c r="K49" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="L49" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="L49" s="15" t="s">
-        <v>90</v>
-      </c>
       <c r="M49" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N49" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
@@ -3149,8 +3173,8 @@
       <c r="B50" s="13">
         <v>330</v>
       </c>
-      <c r="C50" s="13" t="s">
-        <v>55</v>
+      <c r="C50" s="13">
+        <v>0</v>
       </c>
       <c r="D50" s="13">
         <v>120</v>
@@ -3182,10 +3206,10 @@
         <v>50</v>
       </c>
       <c r="M50" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N50" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
@@ -3195,8 +3219,8 @@
       <c r="B51" s="13">
         <v>380</v>
       </c>
-      <c r="C51" s="13" t="s">
-        <v>55</v>
+      <c r="C51" s="13">
+        <v>0</v>
       </c>
       <c r="D51" s="13">
         <v>60</v>
@@ -3222,16 +3246,16 @@
         <v>650</v>
       </c>
       <c r="K51" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="L51" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="L51" s="15" t="s">
-        <v>90</v>
-      </c>
       <c r="M51" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N51" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
@@ -3241,8 +3265,8 @@
       <c r="B52" s="13">
         <v>390</v>
       </c>
-      <c r="C52" s="13" t="s">
-        <v>55</v>
+      <c r="C52" s="13">
+        <v>0</v>
       </c>
       <c r="D52" s="13">
         <v>80</v>
@@ -3274,10 +3298,10 @@
         <v>50</v>
       </c>
       <c r="M52" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N52" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
@@ -3287,8 +3311,8 @@
       <c r="B53" s="13">
         <v>390</v>
       </c>
-      <c r="C53" s="13" t="s">
-        <v>55</v>
+      <c r="C53" s="13">
+        <v>0</v>
       </c>
       <c r="D53" s="13">
         <v>110</v>
@@ -3314,27 +3338,27 @@
         <v>480</v>
       </c>
       <c r="K53" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="L53" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="L53" s="15" t="s">
-        <v>90</v>
-      </c>
       <c r="M53" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N53" s="16" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="12">
         <v>46299</v>
       </c>
       <c r="B54" s="13">
         <v>340</v>
       </c>
-      <c r="C54" s="13" t="s">
-        <v>55</v>
+      <c r="C54" s="13">
+        <v>0</v>
       </c>
       <c r="D54" s="13">
         <v>140</v>
@@ -3360,324 +3384,638 @@
         <v>500</v>
       </c>
       <c r="K54" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="L54" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="L54" s="15" t="s">
-        <v>90</v>
-      </c>
       <c r="M54" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N54" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="12">
         <v>46300</v>
       </c>
-      <c r="B55" s="13"/>
-      <c r="C55" s="13" t="s">
+      <c r="B55" s="13">
+        <v>380</v>
+      </c>
+      <c r="C55" s="13">
+        <v>0</v>
+      </c>
+      <c r="D55" s="13">
+        <v>120</v>
+      </c>
+      <c r="E55" s="13">
+        <v>40</v>
+      </c>
+      <c r="F55" s="13">
+        <v>200</v>
+      </c>
+      <c r="G55" s="13">
+        <v>4</v>
+      </c>
+      <c r="H55" s="13">
+        <v>380</v>
+      </c>
+      <c r="I55" s="14">
+        <f t="shared" si="0"/>
+        <v>1120</v>
+      </c>
+      <c r="J55" s="14">
+        <f t="shared" si="1"/>
+        <v>320</v>
+      </c>
+      <c r="K55" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="L55" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M55" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="N55" s="16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56" s="12">
+        <v>46301</v>
+      </c>
+      <c r="B56" s="13">
+        <v>350</v>
+      </c>
+      <c r="C56" s="13">
+        <v>0</v>
+      </c>
+      <c r="D56" s="13">
+        <v>110</v>
+      </c>
+      <c r="E56" s="13">
+        <v>40</v>
+      </c>
+      <c r="F56" s="13">
+        <v>350</v>
+      </c>
+      <c r="G56" s="13">
+        <v>7</v>
+      </c>
+      <c r="H56" s="13">
+        <v>360</v>
+      </c>
+      <c r="I56" s="14">
+        <f t="shared" si="0"/>
+        <v>1210</v>
+      </c>
+      <c r="J56" s="14">
+        <f t="shared" si="1"/>
+        <v>230</v>
+      </c>
+      <c r="K56" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
-      <c r="I55" s="14" t="str">
+      <c r="L56" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M56" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N56" s="16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A57" s="12">
+        <v>46302</v>
+      </c>
+      <c r="B57" s="13">
+        <v>360</v>
+      </c>
+      <c r="C57" s="13">
+        <v>0</v>
+      </c>
+      <c r="D57" s="13">
+        <v>120</v>
+      </c>
+      <c r="E57" s="13">
+        <v>50</v>
+      </c>
+      <c r="F57" s="13">
+        <v>350</v>
+      </c>
+      <c r="G57" s="13">
+        <v>7</v>
+      </c>
+      <c r="H57" s="13">
+        <v>340</v>
+      </c>
+      <c r="I57" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="14" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J57" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="15"/>
-      <c r="L55" s="15"/>
-      <c r="M55" s="15"/>
-      <c r="N55" s="16"/>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="12"/>
-      <c r="B56" s="13"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="13"/>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="13"/>
-      <c r="H56" s="13"/>
-      <c r="I56" s="14" t="str">
+        <v>220</v>
+      </c>
+      <c r="K57" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="L57" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M57" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N57" s="16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A58" s="12">
+        <v>46303</v>
+      </c>
+      <c r="B58" s="13">
+        <v>370</v>
+      </c>
+      <c r="C58" s="13">
+        <v>0</v>
+      </c>
+      <c r="D58" s="13">
+        <v>90</v>
+      </c>
+      <c r="E58" s="13">
+        <v>30</v>
+      </c>
+      <c r="F58" s="13">
+        <v>0</v>
+      </c>
+      <c r="G58" s="13">
+        <v>0</v>
+      </c>
+      <c r="H58" s="13">
+        <v>320</v>
+      </c>
+      <c r="I58" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="14" t="str">
+        <v>810</v>
+      </c>
+      <c r="J58" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="15"/>
-      <c r="L56" s="15"/>
-      <c r="M56" s="15"/>
-      <c r="N56" s="16"/>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="12"/>
-      <c r="B57" s="13"/>
-      <c r="C57" s="13"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
-      <c r="I57" s="14" t="str">
+        <v>630</v>
+      </c>
+      <c r="K58" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="L58" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M58" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N58" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A59" s="12">
+        <v>46304</v>
+      </c>
+      <c r="B59" s="13">
+        <v>390</v>
+      </c>
+      <c r="C59" s="13">
+        <v>0</v>
+      </c>
+      <c r="D59" s="13">
+        <v>80</v>
+      </c>
+      <c r="E59" s="13">
+        <v>40</v>
+      </c>
+      <c r="F59" s="13">
+        <v>0</v>
+      </c>
+      <c r="G59" s="13">
+        <v>0</v>
+      </c>
+      <c r="H59" s="13">
+        <v>350</v>
+      </c>
+      <c r="I59" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="14" t="str">
+        <v>860</v>
+      </c>
+      <c r="J59" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="15"/>
-      <c r="L57" s="15"/>
-      <c r="M57" s="15"/>
-      <c r="N57" s="16"/>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="12"/>
-      <c r="B58" s="13"/>
-      <c r="C58" s="13"/>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="14" t="str">
+        <v>580</v>
+      </c>
+      <c r="K59" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L59" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M59" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="N59" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A60" s="12">
+        <v>46305</v>
+      </c>
+      <c r="B60" s="13">
+        <v>380</v>
+      </c>
+      <c r="C60" s="13">
+        <v>0</v>
+      </c>
+      <c r="D60" s="13">
+        <v>90</v>
+      </c>
+      <c r="E60" s="13">
+        <v>60</v>
+      </c>
+      <c r="F60" s="13">
+        <v>0</v>
+      </c>
+      <c r="G60" s="13">
+        <v>0</v>
+      </c>
+      <c r="H60" s="13">
+        <v>370</v>
+      </c>
+      <c r="I60" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="14" t="str">
+        <v>900</v>
+      </c>
+      <c r="J60" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="15"/>
-      <c r="L58" s="15"/>
-      <c r="M58" s="15"/>
-      <c r="N58" s="16"/>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="12"/>
-      <c r="B59" s="13"/>
-      <c r="C59" s="13"/>
-      <c r="D59" s="13"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="13"/>
-      <c r="H59" s="13"/>
-      <c r="I59" s="14" t="str">
+        <v>540</v>
+      </c>
+      <c r="K60" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="L60" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M60" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="N60" s="16" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A61" s="12">
+        <v>46306</v>
+      </c>
+      <c r="B61" s="13">
+        <v>340</v>
+      </c>
+      <c r="C61" s="13">
+        <v>0</v>
+      </c>
+      <c r="D61" s="13">
+        <v>180</v>
+      </c>
+      <c r="E61" s="13">
+        <v>40</v>
+      </c>
+      <c r="F61" s="13">
+        <v>0</v>
+      </c>
+      <c r="G61" s="13">
+        <v>0</v>
+      </c>
+      <c r="H61" s="13">
+        <v>350</v>
+      </c>
+      <c r="I61" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="14" t="str">
+        <v>910</v>
+      </c>
+      <c r="J61" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="15"/>
-      <c r="L59" s="15"/>
-      <c r="M59" s="15"/>
-      <c r="N59" s="16"/>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="12"/>
-      <c r="B60" s="13"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="13"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13"/>
-      <c r="I60" s="14" t="str">
+        <v>530</v>
+      </c>
+      <c r="K61" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L61" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M61" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N61" s="16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A62" s="12">
+        <v>46307</v>
+      </c>
+      <c r="B62" s="13">
+        <v>340</v>
+      </c>
+      <c r="C62" s="13">
+        <v>0</v>
+      </c>
+      <c r="D62" s="13">
+        <v>220</v>
+      </c>
+      <c r="E62" s="13">
+        <v>60</v>
+      </c>
+      <c r="F62" s="13">
+        <v>0</v>
+      </c>
+      <c r="G62" s="13">
+        <v>0</v>
+      </c>
+      <c r="H62" s="13">
+        <v>360</v>
+      </c>
+      <c r="I62" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="14" t="str">
+        <v>980</v>
+      </c>
+      <c r="J62" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="15"/>
-      <c r="L60" s="15"/>
-      <c r="M60" s="15"/>
-      <c r="N60" s="16"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="12"/>
-      <c r="B61" s="13"/>
-      <c r="C61" s="13"/>
-      <c r="D61" s="13"/>
-      <c r="E61" s="13"/>
-      <c r="F61" s="13"/>
-      <c r="G61" s="13"/>
-      <c r="H61" s="13"/>
-      <c r="I61" s="14" t="str">
+        <v>460</v>
+      </c>
+      <c r="K62" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L62" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M62" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N62" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A63" s="12">
+        <v>46308</v>
+      </c>
+      <c r="B63" s="13">
+        <v>350</v>
+      </c>
+      <c r="C63" s="13">
+        <v>0</v>
+      </c>
+      <c r="D63" s="13">
+        <v>190</v>
+      </c>
+      <c r="E63" s="13">
+        <v>40</v>
+      </c>
+      <c r="F63" s="13">
+        <v>0</v>
+      </c>
+      <c r="G63" s="13">
+        <v>0</v>
+      </c>
+      <c r="H63" s="13">
+        <v>340</v>
+      </c>
+      <c r="I63" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="14" t="str">
+        <v>920</v>
+      </c>
+      <c r="J63" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="15"/>
-      <c r="L61" s="15"/>
-      <c r="M61" s="15"/>
-      <c r="N61" s="16"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="12"/>
-      <c r="B62" s="13"/>
-      <c r="C62" s="13"/>
-      <c r="D62" s="13"/>
-      <c r="E62" s="13"/>
-      <c r="F62" s="13"/>
-      <c r="G62" s="13"/>
-      <c r="H62" s="13"/>
-      <c r="I62" s="14" t="str">
+        <v>520</v>
+      </c>
+      <c r="K63" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="L63" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M63" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="N63" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A64" s="12">
+        <v>46309</v>
+      </c>
+      <c r="B64" s="13">
+        <v>380</v>
+      </c>
+      <c r="C64" s="13">
+        <v>0</v>
+      </c>
+      <c r="D64" s="13">
+        <v>180</v>
+      </c>
+      <c r="E64" s="13">
+        <v>60</v>
+      </c>
+      <c r="F64" s="13">
+        <v>0</v>
+      </c>
+      <c r="G64" s="13">
+        <v>0</v>
+      </c>
+      <c r="H64" s="13">
+        <v>290</v>
+      </c>
+      <c r="I64" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="14" t="str">
+        <v>910</v>
+      </c>
+      <c r="J64" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="15"/>
-      <c r="L62" s="15"/>
-      <c r="M62" s="15"/>
-      <c r="N62" s="16"/>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="12"/>
-      <c r="B63" s="13"/>
-      <c r="C63" s="13"/>
-      <c r="D63" s="13"/>
-      <c r="E63" s="13"/>
-      <c r="F63" s="13"/>
-      <c r="G63" s="13"/>
-      <c r="H63" s="13"/>
-      <c r="I63" s="14" t="str">
+        <v>530</v>
+      </c>
+      <c r="K64" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="L64" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M64" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="N64" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" s="12">
+        <v>46310</v>
+      </c>
+      <c r="B65" s="13">
+        <v>360</v>
+      </c>
+      <c r="C65" s="13">
+        <v>0</v>
+      </c>
+      <c r="D65" s="13">
+        <v>160</v>
+      </c>
+      <c r="E65" s="13">
+        <v>40</v>
+      </c>
+      <c r="F65" s="13">
+        <v>0</v>
+      </c>
+      <c r="G65" s="13">
+        <v>0</v>
+      </c>
+      <c r="H65" s="13">
+        <v>280</v>
+      </c>
+      <c r="I65" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="14" t="str">
+        <v>840</v>
+      </c>
+      <c r="J65" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="15"/>
-      <c r="L63" s="15"/>
-      <c r="M63" s="15"/>
-      <c r="N63" s="16"/>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="12"/>
-      <c r="B64" s="13"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13"/>
-      <c r="F64" s="13"/>
-      <c r="G64" s="13"/>
-      <c r="H64" s="13"/>
-      <c r="I64" s="14" t="str">
+        <v>600</v>
+      </c>
+      <c r="K65" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L65" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M65" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N65" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A66" s="12">
+        <v>46311</v>
+      </c>
+      <c r="B66" s="13">
+        <v>340</v>
+      </c>
+      <c r="C66" s="13">
+        <v>0</v>
+      </c>
+      <c r="D66" s="13">
+        <v>190</v>
+      </c>
+      <c r="E66" s="13">
+        <v>30</v>
+      </c>
+      <c r="F66" s="13">
+        <v>0</v>
+      </c>
+      <c r="G66" s="13">
+        <v>0</v>
+      </c>
+      <c r="H66" s="13">
+        <v>260</v>
+      </c>
+      <c r="I66" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="14" t="str">
+        <v>820</v>
+      </c>
+      <c r="J66" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="15"/>
-      <c r="L64" s="15"/>
-      <c r="M64" s="15"/>
-      <c r="N64" s="16"/>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="12"/>
-      <c r="B65" s="13"/>
-      <c r="C65" s="13"/>
-      <c r="D65" s="13"/>
-      <c r="E65" s="13"/>
-      <c r="F65" s="13"/>
-      <c r="G65" s="13"/>
-      <c r="H65" s="13"/>
-      <c r="I65" s="14" t="str">
+        <v>620</v>
+      </c>
+      <c r="K66" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L66" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M66" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N66" s="16" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A67" s="12">
+        <v>46312</v>
+      </c>
+      <c r="B67" s="13">
+        <v>350</v>
+      </c>
+      <c r="C67" s="13">
+        <v>0</v>
+      </c>
+      <c r="D67" s="13">
+        <v>150</v>
+      </c>
+      <c r="E67" s="13">
+        <v>40</v>
+      </c>
+      <c r="F67" s="13">
+        <v>0</v>
+      </c>
+      <c r="G67" s="13">
+        <v>0</v>
+      </c>
+      <c r="H67" s="13">
+        <v>250</v>
+      </c>
+      <c r="I67" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="14" t="str">
+        <v>790</v>
+      </c>
+      <c r="J67" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="15"/>
-      <c r="L65" s="15"/>
-      <c r="M65" s="15"/>
-      <c r="N65" s="16"/>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="12"/>
-      <c r="B66" s="13"/>
-      <c r="C66" s="13"/>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13"/>
-      <c r="H66" s="13"/>
-      <c r="I66" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="15"/>
-      <c r="L66" s="15"/>
-      <c r="M66" s="15"/>
-      <c r="N66" s="16"/>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="12"/>
-      <c r="B67" s="13"/>
-      <c r="C67" s="13"/>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="13"/>
-      <c r="H67" s="13"/>
-      <c r="I67" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="15"/>
-      <c r="L67" s="15"/>
-      <c r="M67" s="15"/>
-      <c r="N67" s="16"/>
+        <v>650</v>
+      </c>
+      <c r="K67" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="L67" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M67" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N67" s="16" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="12"/>
-      <c r="B68" s="13"/>
-      <c r="C68" s="13"/>
+      <c r="A68" s="12">
+        <v>46313</v>
+      </c>
+      <c r="B68" s="13">
+        <v>390</v>
+      </c>
+      <c r="C68" s="13">
+        <v>0</v>
+      </c>
       <c r="D68" s="13"/>
       <c r="E68" s="13"/>
       <c r="F68" s="13"/>
       <c r="G68" s="13"/>
       <c r="H68" s="13"/>
-      <c r="I68" s="14" t="str">
+      <c r="I68" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="14" t="str">
+        <v>390</v>
+      </c>
+      <c r="J68" s="14">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1050</v>
       </c>
       <c r="K68" s="15"/>
       <c r="L68" s="15"/>
@@ -3685,9 +4023,13 @@
       <c r="N68" s="16"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="12"/>
+      <c r="A69" s="12">
+        <v>46314</v>
+      </c>
       <c r="B69" s="13"/>
-      <c r="C69" s="13"/>
+      <c r="C69" s="13">
+        <v>0</v>
+      </c>
       <c r="D69" s="13"/>
       <c r="E69" s="13"/>
       <c r="F69" s="13"/>
@@ -3707,9 +4049,13 @@
       <c r="N69" s="16"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="12"/>
+      <c r="A70" s="12">
+        <v>46315</v>
+      </c>
       <c r="B70" s="13"/>
-      <c r="C70" s="13"/>
+      <c r="C70" s="13">
+        <v>0</v>
+      </c>
       <c r="D70" s="13"/>
       <c r="E70" s="13"/>
       <c r="F70" s="13"/>
@@ -3729,9 +4075,13 @@
       <c r="N70" s="16"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="12"/>
+      <c r="A71" s="12">
+        <v>46316</v>
+      </c>
       <c r="B71" s="13"/>
-      <c r="C71" s="13"/>
+      <c r="C71" s="13">
+        <v>0</v>
+      </c>
       <c r="D71" s="13"/>
       <c r="E71" s="13"/>
       <c r="F71" s="13"/>
@@ -3751,9 +4101,13 @@
       <c r="N71" s="16"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="12"/>
+      <c r="A72" s="12">
+        <v>46317</v>
+      </c>
       <c r="B72" s="13"/>
-      <c r="C72" s="13"/>
+      <c r="C72" s="13">
+        <v>0</v>
+      </c>
       <c r="D72" s="13"/>
       <c r="E72" s="13"/>
       <c r="F72" s="13"/>

--- a/12624865.xlsx
+++ b/12624865.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\GIT_DEMO\CAP-776\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A4500F-CE5D-44FB-BE89-982A41294171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D6B49A-FA4B-484B-8ED8-7F893BF799A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="112">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -362,6 +363,15 @@
   </si>
   <si>
     <t>Give last MT.</t>
+  </si>
+  <si>
+    <t>Take rest.</t>
+  </si>
+  <si>
+    <t>Enjoying garba night with friends.</t>
+  </si>
+  <si>
+    <t>Back to basic.</t>
   </si>
 </sst>
 </file>
@@ -4002,77 +4012,135 @@
         <v>390</v>
       </c>
       <c r="C68" s="13">
-        <v>0</v>
-      </c>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
-      <c r="H68" s="13"/>
+        <v>40</v>
+      </c>
+      <c r="D68" s="13">
+        <v>140</v>
+      </c>
+      <c r="E68" s="13">
+        <v>30</v>
+      </c>
+      <c r="F68" s="13">
+        <v>0</v>
+      </c>
+      <c r="G68" s="13">
+        <v>0</v>
+      </c>
+      <c r="H68" s="13">
+        <v>280</v>
+      </c>
       <c r="I68" s="14">
         <f t="shared" si="0"/>
-        <v>390</v>
+        <v>880</v>
       </c>
       <c r="J68" s="14">
         <f t="shared" si="1"/>
-        <v>1050</v>
-      </c>
-      <c r="K68" s="15"/>
-      <c r="L68" s="15"/>
-      <c r="M68" s="15"/>
-      <c r="N68" s="16"/>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+        <v>560</v>
+      </c>
+      <c r="K68" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="L68" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M68" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="N68" s="16" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A69" s="12">
         <v>46314</v>
       </c>
-      <c r="B69" s="13"/>
+      <c r="B69" s="13">
+        <v>380</v>
+      </c>
       <c r="C69" s="13">
         <v>0</v>
       </c>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
-      <c r="H69" s="13"/>
-      <c r="I69" s="14" t="str">
+      <c r="D69" s="13">
+        <v>130</v>
+      </c>
+      <c r="E69" s="13">
+        <v>30</v>
+      </c>
+      <c r="F69" s="13">
+        <v>150</v>
+      </c>
+      <c r="G69" s="13">
+        <v>3</v>
+      </c>
+      <c r="H69" s="13">
+        <v>260</v>
+      </c>
+      <c r="I69" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="14" t="str">
+        <v>950</v>
+      </c>
+      <c r="J69" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="15"/>
-      <c r="L69" s="15"/>
-      <c r="M69" s="15"/>
-      <c r="N69" s="16"/>
+        <v>490</v>
+      </c>
+      <c r="K69" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L69" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M69" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="N69" s="16" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="12">
         <v>46315</v>
       </c>
-      <c r="B70" s="13"/>
+      <c r="B70" s="13">
+        <v>360</v>
+      </c>
       <c r="C70" s="13">
         <v>0</v>
       </c>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="14" t="str">
+      <c r="D70" s="13">
+        <v>120</v>
+      </c>
+      <c r="E70" s="13">
+        <v>20</v>
+      </c>
+      <c r="F70" s="13">
+        <v>0</v>
+      </c>
+      <c r="G70" s="13">
+        <v>0</v>
+      </c>
+      <c r="H70" s="13">
+        <v>250</v>
+      </c>
+      <c r="I70" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J70" s="14" t="str">
+        <v>750</v>
+      </c>
+      <c r="J70" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K70" s="15"/>
-      <c r="L70" s="15"/>
-      <c r="M70" s="15"/>
-      <c r="N70" s="16"/>
+        <v>690</v>
+      </c>
+      <c r="K70" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="L70" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M70" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="N70" s="16" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="12">

--- a/12624865.xlsx
+++ b/12624865.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\GIT_DEMO\CAP-776\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D6B49A-FA4B-484B-8ED8-7F893BF799A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E22E56C-179C-47F0-A763-DB49617B65C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="112">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4142,31 +4141,51 @@
         <v>111</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A71" s="12">
         <v>46316</v>
       </c>
-      <c r="B71" s="13"/>
+      <c r="B71" s="13">
+        <v>350</v>
+      </c>
       <c r="C71" s="13">
         <v>0</v>
       </c>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="14" t="str">
+      <c r="D71" s="13">
+        <v>140</v>
+      </c>
+      <c r="E71" s="13">
+        <v>40</v>
+      </c>
+      <c r="F71" s="13">
+        <v>350</v>
+      </c>
+      <c r="G71" s="13">
+        <v>7</v>
+      </c>
+      <c r="H71" s="13">
+        <v>240</v>
+      </c>
+      <c r="I71" s="14">
         <f t="shared" ref="I71:I134" si="2">IF(SUM(B71:F71,H71)=0,"",SUM(B71:F71,H71))</f>
-        <v/>
-      </c>
-      <c r="J71" s="14" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J71" s="14">
         <f t="shared" ref="J71:J134" si="3">IF(I71="","",1440-I71)</f>
-        <v/>
-      </c>
-      <c r="K71" s="15"/>
-      <c r="L71" s="15"/>
-      <c r="M71" s="15"/>
-      <c r="N71" s="16"/>
+        <v>320</v>
+      </c>
+      <c r="K71" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L71" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M71" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="N71" s="16" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="12">

--- a/12624865.xlsx
+++ b/12624865.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\GIT_DEMO\CAP-776\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E22E56C-179C-47F0-A763-DB49617B65C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD4FC2F3-9416-4816-865D-EF7C0947D403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -349,18 +349,6 @@
     <t>Mid-Term was started.</t>
   </si>
   <si>
-    <t>Give 3 MT.</t>
-  </si>
-  <si>
-    <t>Give 2 MT.</t>
-  </si>
-  <si>
-    <t>Give 4 MT.</t>
-  </si>
-  <si>
-    <t>Give 5 MT.</t>
-  </si>
-  <si>
     <t>Give last MT.</t>
   </si>
   <si>
@@ -371,6 +359,24 @@
   </si>
   <si>
     <t>Back to basic.</t>
+  </si>
+  <si>
+    <t>Give 2nd MT.</t>
+  </si>
+  <si>
+    <t>Give 3rd MT.</t>
+  </si>
+  <si>
+    <t>Give 4th MT.</t>
+  </si>
+  <si>
+    <t>Give 5th MT.</t>
+  </si>
+  <si>
+    <t>Studied analytical skills</t>
+  </si>
+  <si>
+    <t>Focused on skills!!</t>
   </si>
 </sst>
 </file>
@@ -3816,7 +3822,7 @@
         <v>56</v>
       </c>
       <c r="N63" s="16" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
@@ -3862,7 +3868,7 @@
         <v>56</v>
       </c>
       <c r="N64" s="16" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
@@ -3908,7 +3914,7 @@
         <v>51</v>
       </c>
       <c r="N65" s="16" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
@@ -3954,7 +3960,7 @@
         <v>51</v>
       </c>
       <c r="N66" s="16" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
@@ -4000,7 +4006,7 @@
         <v>51</v>
       </c>
       <c r="N67" s="16" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
@@ -4046,7 +4052,7 @@
         <v>56</v>
       </c>
       <c r="N68" s="16" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="69" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -4092,7 +4098,7 @@
         <v>60</v>
       </c>
       <c r="N69" s="16" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
@@ -4138,7 +4144,7 @@
         <v>56</v>
       </c>
       <c r="N70" s="16" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="71" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -4187,100 +4193,194 @@
         <v>75</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A72" s="12">
         <v>46317</v>
       </c>
-      <c r="B72" s="13"/>
+      <c r="B72" s="13">
+        <v>340</v>
+      </c>
       <c r="C72" s="13">
         <v>0</v>
       </c>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="14" t="str">
+      <c r="D72" s="13">
+        <v>110</v>
+      </c>
+      <c r="E72" s="13">
+        <v>25</v>
+      </c>
+      <c r="F72" s="13">
+        <v>200</v>
+      </c>
+      <c r="G72" s="13">
+        <v>4</v>
+      </c>
+      <c r="H72" s="13">
+        <v>220</v>
+      </c>
+      <c r="I72" s="14">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="14" t="str">
+        <v>895</v>
+      </c>
+      <c r="J72" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="15"/>
-      <c r="L72" s="15"/>
-      <c r="M72" s="15"/>
-      <c r="N72" s="16"/>
+        <v>545</v>
+      </c>
+      <c r="K72" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L72" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M72" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N72" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="12"/>
-      <c r="B73" s="13"/>
-      <c r="C73" s="13"/>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="14" t="str">
+      <c r="A73" s="12">
+        <v>46318</v>
+      </c>
+      <c r="B73" s="13">
+        <v>350</v>
+      </c>
+      <c r="C73" s="13">
+        <v>20</v>
+      </c>
+      <c r="D73" s="13">
+        <v>90</v>
+      </c>
+      <c r="E73" s="13">
+        <v>20</v>
+      </c>
+      <c r="F73" s="13">
+        <v>250</v>
+      </c>
+      <c r="G73" s="13">
+        <v>5</v>
+      </c>
+      <c r="H73" s="13">
+        <v>240</v>
+      </c>
+      <c r="I73" s="14">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="14" t="str">
+        <v>970</v>
+      </c>
+      <c r="J73" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="15"/>
-      <c r="L73" s="15"/>
-      <c r="M73" s="15"/>
-      <c r="N73" s="16"/>
+        <v>470</v>
+      </c>
+      <c r="K73" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="L73" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M73" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N73" s="16" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="12"/>
-      <c r="B74" s="13"/>
-      <c r="C74" s="13"/>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="14" t="str">
+      <c r="A74" s="12">
+        <v>46319</v>
+      </c>
+      <c r="B74" s="13">
+        <v>320</v>
+      </c>
+      <c r="C74" s="13">
+        <v>30</v>
+      </c>
+      <c r="D74" s="13">
+        <v>140</v>
+      </c>
+      <c r="E74" s="13">
+        <v>30</v>
+      </c>
+      <c r="F74" s="13">
+        <v>0</v>
+      </c>
+      <c r="G74" s="13">
+        <v>0</v>
+      </c>
+      <c r="H74" s="13">
+        <v>230</v>
+      </c>
+      <c r="I74" s="14">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="14" t="str">
+        <v>750</v>
+      </c>
+      <c r="J74" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="15"/>
-      <c r="L74" s="15"/>
-      <c r="M74" s="15"/>
-      <c r="N74" s="16"/>
+        <v>690</v>
+      </c>
+      <c r="K74" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="L74" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M74" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="N74" s="16" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="12"/>
-      <c r="B75" s="13"/>
-      <c r="C75" s="13"/>
-      <c r="D75" s="13"/>
-      <c r="E75" s="13"/>
-      <c r="F75" s="13"/>
-      <c r="G75" s="13"/>
-      <c r="H75" s="13"/>
-      <c r="I75" s="14" t="str">
+      <c r="A75" s="12">
+        <v>46320</v>
+      </c>
+      <c r="B75" s="13">
+        <v>340</v>
+      </c>
+      <c r="C75" s="13">
+        <v>40</v>
+      </c>
+      <c r="D75" s="13">
+        <v>120</v>
+      </c>
+      <c r="E75" s="13">
+        <v>60</v>
+      </c>
+      <c r="F75" s="13">
+        <v>0</v>
+      </c>
+      <c r="G75" s="13">
+        <v>0</v>
+      </c>
+      <c r="H75" s="13">
+        <v>280</v>
+      </c>
+      <c r="I75" s="14">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="14" t="str">
+        <v>840</v>
+      </c>
+      <c r="J75" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="15"/>
-      <c r="L75" s="15"/>
-      <c r="M75" s="15"/>
-      <c r="N75" s="16"/>
+        <v>600</v>
+      </c>
+      <c r="K75" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L75" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M75" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N75" s="16" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" s="12"/>
+      <c r="A76" s="12">
+        <v>46321</v>
+      </c>
       <c r="B76" s="13"/>
       <c r="C76" s="13"/>
       <c r="D76" s="13"/>
@@ -4302,7 +4402,9 @@
       <c r="N76" s="16"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="12"/>
+      <c r="A77" s="12">
+        <v>46322</v>
+      </c>
       <c r="B77" s="13"/>
       <c r="C77" s="13"/>
       <c r="D77" s="13"/>
@@ -4324,7 +4426,9 @@
       <c r="N77" s="16"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" s="12"/>
+      <c r="A78" s="12">
+        <v>46323</v>
+      </c>
       <c r="B78" s="13"/>
       <c r="C78" s="13"/>
       <c r="D78" s="13"/>
@@ -4346,7 +4450,9 @@
       <c r="N78" s="16"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A79" s="12"/>
+      <c r="A79" s="12">
+        <v>46324</v>
+      </c>
       <c r="B79" s="13"/>
       <c r="C79" s="13"/>
       <c r="D79" s="13"/>
@@ -4368,7 +4474,9 @@
       <c r="N79" s="16"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A80" s="12"/>
+      <c r="A80" s="12">
+        <v>46325</v>
+      </c>
       <c r="B80" s="13"/>
       <c r="C80" s="13"/>
       <c r="D80" s="13"/>
@@ -4390,7 +4498,9 @@
       <c r="N80" s="16"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A81" s="12"/>
+      <c r="A81" s="12">
+        <v>46326</v>
+      </c>
       <c r="B81" s="13"/>
       <c r="C81" s="13"/>
       <c r="D81" s="13"/>
@@ -4412,7 +4522,9 @@
       <c r="N81" s="16"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A82" s="12"/>
+      <c r="A82" s="12">
+        <v>46327</v>
+      </c>
       <c r="B82" s="13"/>
       <c r="C82" s="13"/>
       <c r="D82" s="13"/>
@@ -4434,7 +4546,9 @@
       <c r="N82" s="16"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A83" s="12"/>
+      <c r="A83" s="12">
+        <v>46328</v>
+      </c>
       <c r="B83" s="13"/>
       <c r="C83" s="13"/>
       <c r="D83" s="13"/>
@@ -4456,7 +4570,9 @@
       <c r="N83" s="16"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A84" s="12"/>
+      <c r="A84" s="12">
+        <v>46329</v>
+      </c>
       <c r="B84" s="13"/>
       <c r="C84" s="13"/>
       <c r="D84" s="13"/>

--- a/12624865.xlsx
+++ b/12624865.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\GIT_DEMO\CAP-776\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD4FC2F3-9416-4816-865D-EF7C0947D403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19037E3D-F729-4028-8CEF-2246D3D6495A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="116">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -377,6 +377,12 @@
   </si>
   <si>
     <t>Focused on skills!!</t>
+  </si>
+  <si>
+    <t>Revised concepts and stayed consistent with my routine</t>
+  </si>
+  <si>
+    <t>Attended classes, practiced coding, and made steady progress.</t>
   </si>
 </sst>
 </file>
@@ -4377,53 +4383,97 @@
         <v>85</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A76" s="12">
         <v>46321</v>
       </c>
-      <c r="B76" s="13"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="13"/>
-      <c r="E76" s="13"/>
-      <c r="F76" s="13"/>
-      <c r="G76" s="13"/>
-      <c r="H76" s="13"/>
-      <c r="I76" s="14" t="str">
+      <c r="B76" s="13">
+        <v>360</v>
+      </c>
+      <c r="C76" s="13">
+        <v>0</v>
+      </c>
+      <c r="D76" s="13">
+        <v>160</v>
+      </c>
+      <c r="E76" s="13">
+        <v>50</v>
+      </c>
+      <c r="F76" s="13">
+        <v>0</v>
+      </c>
+      <c r="G76" s="13">
+        <v>0</v>
+      </c>
+      <c r="H76" s="13">
+        <v>280</v>
+      </c>
+      <c r="I76" s="14">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="14" t="str">
+        <v>850</v>
+      </c>
+      <c r="J76" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K76" s="15"/>
-      <c r="L76" s="15"/>
-      <c r="M76" s="15"/>
-      <c r="N76" s="16"/>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+        <v>590</v>
+      </c>
+      <c r="K76" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="L76" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M76" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N76" s="16" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="12">
         <v>46322</v>
       </c>
-      <c r="B77" s="13"/>
-      <c r="C77" s="13"/>
-      <c r="D77" s="13"/>
-      <c r="E77" s="13"/>
-      <c r="F77" s="13"/>
-      <c r="G77" s="13"/>
-      <c r="H77" s="13"/>
-      <c r="I77" s="14" t="str">
+      <c r="B77" s="13">
+        <v>350</v>
+      </c>
+      <c r="C77" s="13">
+        <v>0</v>
+      </c>
+      <c r="D77" s="13">
+        <v>180</v>
+      </c>
+      <c r="E77" s="13">
+        <v>40</v>
+      </c>
+      <c r="F77" s="13">
+        <v>200</v>
+      </c>
+      <c r="G77" s="13">
+        <v>4</v>
+      </c>
+      <c r="H77" s="13">
+        <v>260</v>
+      </c>
+      <c r="I77" s="14">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J77" s="14" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J77" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K77" s="15"/>
-      <c r="L77" s="15"/>
-      <c r="M77" s="15"/>
-      <c r="N77" s="16"/>
+        <v>410</v>
+      </c>
+      <c r="K77" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L77" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M77" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="N77" s="16" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="12">

--- a/12624865.xlsx
+++ b/12624865.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\GIT_DEMO\CAP-776\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19037E3D-F729-4028-8CEF-2246D3D6495A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9700798F-A0BF-4958-A1CF-848384E4B28D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="118">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -383,6 +383,12 @@
   </si>
   <si>
     <t>Attended classes, practiced coding, and made steady progress.</t>
+  </si>
+  <si>
+    <t>Focused on learning new concepts and improving my coding skills.</t>
+  </si>
+  <si>
+    <t>Balanced academics and personal time while staying productive.</t>
   </si>
 </sst>
 </file>
@@ -4475,53 +4481,97 @@
         <v>115</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A78" s="12">
         <v>46323</v>
       </c>
-      <c r="B78" s="13"/>
-      <c r="C78" s="13"/>
-      <c r="D78" s="13"/>
-      <c r="E78" s="13"/>
-      <c r="F78" s="13"/>
-      <c r="G78" s="13"/>
-      <c r="H78" s="13"/>
-      <c r="I78" s="14" t="str">
+      <c r="B78" s="13">
+        <v>340</v>
+      </c>
+      <c r="C78" s="13">
+        <v>0</v>
+      </c>
+      <c r="D78" s="13">
+        <v>160</v>
+      </c>
+      <c r="E78" s="13">
+        <v>30</v>
+      </c>
+      <c r="F78" s="13">
+        <v>300</v>
+      </c>
+      <c r="G78" s="13">
+        <v>6</v>
+      </c>
+      <c r="H78" s="13">
+        <v>290</v>
+      </c>
+      <c r="I78" s="14">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J78" s="14" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J78" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K78" s="15"/>
-      <c r="L78" s="15"/>
-      <c r="M78" s="15"/>
-      <c r="N78" s="16"/>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+        <v>320</v>
+      </c>
+      <c r="K78" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="L78" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M78" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N78" s="16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="12">
         <v>46324</v>
       </c>
-      <c r="B79" s="13"/>
-      <c r="C79" s="13"/>
-      <c r="D79" s="13"/>
-      <c r="E79" s="13"/>
-      <c r="F79" s="13"/>
-      <c r="G79" s="13"/>
-      <c r="H79" s="13"/>
-      <c r="I79" s="14" t="str">
+      <c r="B79" s="13">
+        <v>360</v>
+      </c>
+      <c r="C79" s="13">
+        <v>20</v>
+      </c>
+      <c r="D79" s="13">
+        <v>130</v>
+      </c>
+      <c r="E79" s="13">
+        <v>40</v>
+      </c>
+      <c r="F79" s="13">
+        <v>200</v>
+      </c>
+      <c r="G79" s="13">
+        <v>4</v>
+      </c>
+      <c r="H79" s="13">
+        <v>320</v>
+      </c>
+      <c r="I79" s="14">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J79" s="14" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J79" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K79" s="15"/>
-      <c r="L79" s="15"/>
-      <c r="M79" s="15"/>
-      <c r="N79" s="16"/>
+        <v>370</v>
+      </c>
+      <c r="K79" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="L79" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M79" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N79" s="16" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="12">
